--- a/data/7Juni-Gold_Diggers-v-89ers.xlsx
+++ b/data/7Juni-Gold_Diggers-v-89ers.xlsx
@@ -253,7 +253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O126"/>
   <sheetData>
     <row r="1">
@@ -356,8 +356,10 @@
       <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>17</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DCLM</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -638,8 +640,10 @@
       <c r="D37" t="s">
         <v>16</v>
       </c>
-      <c r="E37" t="s">
-        <v>17</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DCLM</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -695,8 +699,10 @@
       <c r="D43" t="s">
         <v>16</v>
       </c>
-      <c r="E43" t="s">
-        <v>29</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>UCDNLN</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1028,8 +1034,10 @@
       <c r="G70" t="s">
         <v>16</v>
       </c>
-      <c r="H70" t="s">
-        <v>52</v>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>BCDC</t>
+        </is>
       </c>
       <c r="I70" t="s">
         <v>18</v>
@@ -1274,8 +1282,10 @@
       <c r="D94" t="s">
         <v>16</v>
       </c>
-      <c r="E94" t="s">
-        <v>58</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DCLC</t>
+        </is>
       </c>
       <c r="I94" t="s">
         <v>59</v>
@@ -1652,8 +1662,10 @@
       <c r="D124" t="s">
         <v>16</v>
       </c>
-      <c r="E124" t="s">
-        <v>77</v>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>DCSC</t>
+        </is>
       </c>
       <c r="I124" t="s">
         <v>18</v>
